--- a/Scripts_inesdattatreya/fig_output/beschrijvendestatistieken_metQ9/descriptives_means_per_class_incl_responsibility_allocation.xlsx
+++ b/Scripts_inesdattatreya/fig_output/beschrijvendestatistieken_metQ9/descriptives_means_per_class_incl_responsibility_allocation.xlsx
@@ -430,7 +430,7 @@
         <v>2.192307692307693</v>
       </c>
       <c r="F2">
-        <v>3.807692307692307</v>
+        <v>3.807692307692308</v>
       </c>
       <c r="G2">
         <v>3.557692307692307</v>
@@ -442,7 +442,7 @@
         <v>3.788461538461538</v>
       </c>
       <c r="J2">
-        <v>3.192307692307693</v>
+        <v>3.192307692307692</v>
       </c>
       <c r="K2">
         <v>1.822222222222222</v>
@@ -498,7 +498,7 @@
         <v>1.6125</v>
       </c>
       <c r="D4">
-        <v>2.0125</v>
+        <v>2.012500000000001</v>
       </c>
       <c r="E4">
         <v>1.375</v>
@@ -516,7 +516,7 @@
         <v>3.1375</v>
       </c>
       <c r="J4">
-        <v>2.6375</v>
+        <v>2.637500000000001</v>
       </c>
       <c r="K4">
         <v>1.791666666666667</v>
